--- a/src/src/main/webapp/portal/asset/contract/contractImport/APM_ContractItem_Service_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/contract/contractImport/APM_ContractItem_Service_Template.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{30404FA7-D76D-41CA-97B6-F86C9CEAA877}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{26B91993-E99B-4618-B9E3-53D143304DE5}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ContractItem List" sheetId="1" r:id="rId1"/>
+    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>合同UID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -29,12 +30,21 @@
     <t>相关设备UID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>填写说明</t>
+  </si>
+  <si>
+    <t>1. 合同uid 可通过导出合同， 在导出的Excel中取到uid</t>
+  </si>
+  <si>
+    <t>2. 相关设备uid 可通过导出资产，在导出的Excel中取到uid</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,16 +59,36 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -66,13 +96,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -356,15 +459,15 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -373,4 +476,83 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4DB3CD3-EC18-4D87-920F-4C74B5109A1C}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>